--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCL.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCL.xlsx
@@ -1219,13 +1219,13 @@
         <v>74.2</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="3">
@@ -1238,13 +1238,13 @@
         <v>108.6</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="4">
@@ -1257,13 +1257,13 @@
         <v>88.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="5">
@@ -1276,13 +1276,13 @@
         <v>20.4</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="6">
@@ -1295,7 +1295,7 @@
         <v>18.7</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -1352,13 +1352,13 @@
         <v>15.7</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="10">
